--- a/data/trans_camb/IP18A03-Edad-trans_camb.xlsx
+++ b/data/trans_camb/IP18A03-Edad-trans_camb.xlsx
@@ -523,7 +523,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que su última consulta al médico fue por diagnóstico y vacunación</t>
+          <t>Menores que su última consulta al médico fue por diagnóstico y tratamiento</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -634,7 +634,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>-12,68</t>
+          <t>12,7</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -649,7 +649,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>-6,45</t>
+          <t>28,6</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>-9,53</t>
+          <t>20,98</t>
         </is>
       </c>
     </row>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-9,3; 12,31</t>
+          <t>-9,41; 11,57</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-17,39; 2,57</t>
+          <t>-16,92; 3,53</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-30,06; 6,94</t>
+          <t>-6,71; 31,83</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>2,73; 23,25</t>
+          <t>2,57; 22,33</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-9,28; 10,66</t>
+          <t>-9,66; 10,44</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-23,09; 11,63</t>
+          <t>12,29; 44,23</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-0,45; 14,6</t>
+          <t>-0,4; 14,07</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-9,83; 5,28</t>
+          <t>-9,78; 4,67</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-21,68; 4,47</t>
+          <t>9,15; 34,06</t>
         </is>
       </c>
     </row>
@@ -740,7 +740,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>-28,32%</t>
+          <t>28,37%</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -755,7 +755,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>-18,48%</t>
+          <t>81,98%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>-24,02%</t>
+          <t>52,86%</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-17,67; 32,09</t>
+          <t>-18,01; 29,67</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-35,6; 6,46</t>
+          <t>-34,23; 9,34</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-61,84; 17,08</t>
+          <t>-14,92; 75,06</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>6,87; 78,99</t>
+          <t>6,74; 73,9</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-23,02; 36,28</t>
+          <t>-23,7; 33,78</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-60,37; 36,13</t>
+          <t>34,31; 151,77</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-0,76; 42,47</t>
+          <t>-0,96; 40,26</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-22,56; 15,43</t>
+          <t>-22,74; 13,05</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-52,47; 12,96</t>
+          <t>21,43; 91,75</t>
         </is>
       </c>
     </row>
@@ -850,7 +850,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>-21,2</t>
+          <t>23,87</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -865,7 +865,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>-37,66</t>
+          <t>14,82</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>-29,89</t>
+          <t>19,21</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-4,24; 10,29</t>
+          <t>-3,68; 11,35</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1,88; 16,1</t>
+          <t>1,78; 17,21</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-36,08; -4,99</t>
+          <t>9,05; 34,35</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-6,79; 6,82</t>
+          <t>-6,55; 7,5</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-7,47; 6,59</t>
+          <t>-7,09; 6,23</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-49,77; -22,03</t>
+          <t>2,21; 26,12</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-2,78; 7,33</t>
+          <t>-2,98; 7,9</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-0,69; 9,85</t>
+          <t>-0,62; 9,35</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-40,13; -19,41</t>
+          <t>9,53; 27,13</t>
         </is>
       </c>
     </row>
@@ -956,7 +956,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>-34,65%</t>
+          <t>39,0%</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -971,7 +971,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>-55,71%</t>
+          <t>21,92%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>-46,41%</t>
+          <t>29,83%</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-6,73; 18,13</t>
+          <t>-5,5; 19,91</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>2,9; 28,19</t>
+          <t>2,67; 30,23</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-57,89; -8,08</t>
+          <t>15,7; 60,3</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-9,5; 10,58</t>
+          <t>-9,23; 11,69</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-10,49; 10,15</t>
+          <t>-10,04; 9,87</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-72,84; -33,46</t>
+          <t>3,37; 40,35</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-4,25; 11,8</t>
+          <t>-4,41; 12,81</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-0,99; 15,88</t>
+          <t>-0,92; 15,35</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-61,36; -30,03</t>
+          <t>14,37; 42,86</t>
         </is>
       </c>
     </row>
@@ -1066,7 +1066,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>-26,12</t>
+          <t>12,25</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>-39,18</t>
+          <t>11,75</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>-33,06</t>
+          <t>12,1</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-4,53; 14,98</t>
+          <t>-4,81; 14,77</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-3,86; 14,28</t>
+          <t>-3,24; 15,75</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-43,12; -2,02</t>
+          <t>-4,87; 25,0</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-7,79; 10,74</t>
+          <t>-8,0; 10,55</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-5,48; 11,5</t>
+          <t>-5,49; 12,24</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-53,97; -21,56</t>
+          <t>-1,72; 24,41</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-3,23; 10,16</t>
+          <t>-2,99; 10,14</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-1,91; 10,67</t>
+          <t>-1,91; 10,64</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-45,58; -20,13</t>
+          <t>1,22; 21,06</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1172,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>-39,81%</t>
+          <t>18,67%</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1187,7 +1187,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>-54,6%</t>
+          <t>16,38%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>-48,05%</t>
+          <t>17,58%</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-6,26; 25,18</t>
+          <t>-6,75; 24,7</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-5,55; 24,0</t>
+          <t>-4,54; 26,64</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-64,62; -3,43</t>
+          <t>-6,86; 41,3</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-10,0; 16,1</t>
+          <t>-10,48; 16,43</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-6,99; 17,08</t>
+          <t>-7,14; 18,31</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-73,1; -31,43</t>
+          <t>-2,71; 35,65</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-4,52; 15,55</t>
+          <t>-4,22; 15,28</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-2,64; 16,39</t>
+          <t>-2,64; 16,58</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-64,43; -30,23</t>
+          <t>1,99; 31,55</t>
         </is>
       </c>
     </row>
@@ -1282,7 +1282,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>-41,03</t>
+          <t>5,15</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -1297,7 +1297,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>-38,93</t>
+          <t>6,92</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>-39,84</t>
+          <t>6,13</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-6,11; 10,37</t>
+          <t>-5,39; 10,93</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-7,59; 8,47</t>
+          <t>-8,57; 8,78</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-57,39; -22,25</t>
+          <t>-13,46; 17,77</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-10,79; 5,53</t>
+          <t>-10,15; 6,43</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-9,08; 7,32</t>
+          <t>-8,45; 7,46</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-53,73; -21,07</t>
+          <t>-6,53; 17,35</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-5,59; 5,57</t>
+          <t>-5,12; 5,66</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-6,32; 5,11</t>
+          <t>-6,5; 5,4</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-50,68; -28,22</t>
+          <t>-3,83; 14,33</t>
         </is>
       </c>
     </row>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>-54,82%</t>
+          <t>6,88%</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -1403,7 +1403,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>-52,83%</t>
+          <t>9,39%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>-53,66%</t>
+          <t>8,26%</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-7,63; 14,42</t>
+          <t>-6,82; 15,72</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-9,67; 12,2</t>
+          <t>-10,98; 12,47</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-75,83; -30,69</t>
+          <t>-17,01; 24,26</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-14,16; 7,68</t>
+          <t>-12,95; 9,36</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-11,6; 10,36</t>
+          <t>-11,06; 10,72</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-70,82; -28,86</t>
+          <t>-8,6; 24,97</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-7,2; 7,79</t>
+          <t>-6,72; 7,79</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-8,31; 7,07</t>
+          <t>-8,45; 7,71</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-67,26; -38,66</t>
+          <t>-5,12; 19,77</t>
         </is>
       </c>
     </row>
@@ -1498,7 +1498,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>-25,77</t>
+          <t>14,29</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -1513,7 +1513,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>-32,33</t>
+          <t>15,12</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>-29,4</t>
+          <t>14,85</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-2,24; 6,68</t>
+          <t>-2,05; 6,82</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-2,03; 6,82</t>
+          <t>-2,34; 6,79</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-34,43; -16,73</t>
+          <t>6,32; 21,55</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-2,68; 5,79</t>
+          <t>-2,49; 5,83</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-4,07; 4,65</t>
+          <t>-3,93; 4,69</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-39,51; -24,62</t>
+          <t>8,26; 20,89</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-1,24; 4,86</t>
+          <t>-1,24; 4,89</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-1,62; 4,55</t>
+          <t>-1,67; 4,41</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-35,59; -22,61</t>
+          <t>9,67; 19,68</t>
         </is>
       </c>
     </row>
@@ -1604,7 +1604,7 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>-41,03%</t>
+          <t>22,75%</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
@@ -1619,7 +1619,7 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>-50,24%</t>
+          <t>23,5%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -1634,7 +1634,7 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>-46,23%</t>
+          <t>23,35%</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-3,44; 10,87</t>
+          <t>-3,25; 11,21</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-3,09; 11,3</t>
+          <t>-3,4; 11,38</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-53,83; -27,21</t>
+          <t>9,46; 34,97</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-4,09; 9,29</t>
+          <t>-3,8; 9,42</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-6,16; 7,54</t>
+          <t>-5,82; 7,59</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-60,72; -38,42</t>
+          <t>12,52; 33,61</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-1,9; 7,83</t>
+          <t>-1,69; 8,11</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-2,5; 7,31</t>
+          <t>-2,53; 7,15</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-55,46; -36,14</t>
+          <t>15,1; 31,39</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/IP18A03-Edad-trans_camb.xlsx
+++ b/data/trans_camb/IP18A03-Edad-trans_camb.xlsx
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-9,41; 11,57</t>
+          <t>-8,87; 12,1</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-16,92; 3,53</t>
+          <t>-17,88; 3,01</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-6,71; 31,83</t>
+          <t>-9,17; 31,81</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>2,57; 22,33</t>
+          <t>1,83; 22,27</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-9,66; 10,44</t>
+          <t>-9,36; 10,36</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>12,29; 44,23</t>
+          <t>9,9; 43,78</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-0,4; 14,07</t>
+          <t>0,46; 14,81</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-9,78; 4,67</t>
+          <t>-9,46; 4,88</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>9,15; 34,06</t>
+          <t>7,99; 33,8</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-18,01; 29,67</t>
+          <t>-17,51; 31,24</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-34,23; 9,34</t>
+          <t>-34,92; 8,04</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-14,92; 75,06</t>
+          <t>-17,87; 76,75</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>6,74; 73,9</t>
+          <t>4,04; 75,31</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-23,7; 33,78</t>
+          <t>-23,12; 34,46</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>34,31; 151,77</t>
+          <t>27,73; 143,56</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-0,96; 40,26</t>
+          <t>1,05; 41,44</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-22,74; 13,05</t>
+          <t>-21,94; 13,28</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>21,43; 91,75</t>
+          <t>19,2; 92,22</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-3,68; 11,35</t>
+          <t>-3,39; 11,91</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1,78; 17,21</t>
+          <t>1,66; 16,48</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>9,05; 34,35</t>
+          <t>9,16; 34,01</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-6,55; 7,5</t>
+          <t>-6,98; 7,19</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-7,09; 6,23</t>
+          <t>-7,74; 6,29</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>2,21; 26,12</t>
+          <t>0,36; 24,99</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-2,98; 7,9</t>
+          <t>-2,89; 6,75</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-0,62; 9,35</t>
+          <t>-0,65; 9,38</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>9,53; 27,13</t>
+          <t>10,12; 26,65</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-5,5; 19,91</t>
+          <t>-4,83; 21,21</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>2,67; 30,23</t>
+          <t>2,48; 28,43</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>15,7; 60,3</t>
+          <t>16,62; 59,89</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-9,23; 11,69</t>
+          <t>-9,64; 11,17</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-10,04; 9,87</t>
+          <t>-10,8; 9,69</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>3,37; 40,35</t>
+          <t>0,58; 38,07</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-4,41; 12,81</t>
+          <t>-4,35; 10,69</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-0,92; 15,35</t>
+          <t>-0,86; 15,39</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>14,37; 42,86</t>
+          <t>15,57; 43,24</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-4,81; 14,77</t>
+          <t>-3,82; 15,48</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-3,24; 15,75</t>
+          <t>-3,48; 15,36</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-4,87; 25,0</t>
+          <t>-3,38; 25,63</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-8,0; 10,55</t>
+          <t>-7,24; 10,63</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-5,49; 12,24</t>
+          <t>-5,55; 11,93</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-1,72; 24,41</t>
+          <t>-2,09; 21,92</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-2,99; 10,14</t>
+          <t>-3,02; 10,03</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-1,91; 10,64</t>
+          <t>-2,28; 10,62</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>1,22; 21,06</t>
+          <t>0,87; 21,33</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-6,75; 24,7</t>
+          <t>-5,43; 25,84</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-4,54; 26,64</t>
+          <t>-4,89; 26,48</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-6,86; 41,3</t>
+          <t>-4,89; 42,72</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-10,48; 16,43</t>
+          <t>-9,43; 16,28</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-7,14; 18,31</t>
+          <t>-7,18; 17,58</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-2,71; 35,65</t>
+          <t>-2,68; 32,68</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-4,22; 15,28</t>
+          <t>-4,17; 15,55</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-2,64; 16,58</t>
+          <t>-3,13; 16,61</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>1,99; 31,55</t>
+          <t>1,45; 32,73</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-5,39; 10,93</t>
+          <t>-5,1; 10,89</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-8,57; 8,78</t>
+          <t>-7,89; 8,95</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-13,46; 17,77</t>
+          <t>-13,12; 18,4</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-10,15; 6,43</t>
+          <t>-9,52; 6,32</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-8,45; 7,46</t>
+          <t>-8,38; 8,52</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-6,53; 17,35</t>
+          <t>-5,56; 17,56</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-5,12; 5,66</t>
+          <t>-5,43; 6,0</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-6,5; 5,4</t>
+          <t>-5,67; 5,45</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-3,83; 14,33</t>
+          <t>-3,61; 15,53</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-6,82; 15,72</t>
+          <t>-6,63; 15,51</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-10,98; 12,47</t>
+          <t>-10,19; 12,83</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-17,01; 24,26</t>
+          <t>-16,39; 25,72</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-12,95; 9,36</t>
+          <t>-12,33; 9,06</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-11,06; 10,72</t>
+          <t>-10,79; 12,23</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-8,6; 24,97</t>
+          <t>-6,99; 25,08</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-6,72; 7,79</t>
+          <t>-7,14; 8,38</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-8,45; 7,71</t>
+          <t>-7,54; 7,62</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-5,12; 19,77</t>
+          <t>-4,61; 21,69</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-2,05; 6,82</t>
+          <t>-2,13; 6,94</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-2,34; 6,79</t>
+          <t>-1,84; 6,97</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>6,32; 21,55</t>
+          <t>5,84; 21,44</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-2,49; 5,83</t>
+          <t>-2,84; 5,89</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-3,93; 4,69</t>
+          <t>-3,48; 4,77</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>8,26; 20,89</t>
+          <t>8,61; 21,31</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-1,24; 4,89</t>
+          <t>-1,12; 4,85</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-1,67; 4,41</t>
+          <t>-1,65; 4,18</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>9,67; 19,68</t>
+          <t>9,58; 20,05</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-3,25; 11,21</t>
+          <t>-3,29; 11,35</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-3,4; 11,38</t>
+          <t>-2,84; 11,62</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>9,46; 34,97</t>
+          <t>9,32; 35,39</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-3,8; 9,42</t>
+          <t>-4,27; 9,44</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-5,82; 7,59</t>
+          <t>-5,33; 7,64</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>12,52; 33,61</t>
+          <t>13,08; 34,03</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-1,69; 8,11</t>
+          <t>-1,7; 7,83</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-2,53; 7,15</t>
+          <t>-2,56; 6,7</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>15,1; 31,39</t>
+          <t>14,58; 31,81</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/IP18A03-Edad-trans_camb.xlsx
+++ b/data/trans_camb/IP18A03-Edad-trans_camb.xlsx
@@ -523,20 +523,20 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que su última consulta al médico fue por diagnóstico y tratamiento</t>
+          <t>Menores cuya última consulta médica fue por diagnóstico y tratamiento</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="n"/>
       <c r="F1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="G1" s="3" t="n"/>
@@ -624,32 +624,32 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>12,36</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>1,13</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>28,41</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
           <t>1,54</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="G4" s="2" t="inlineStr">
         <is>
           <t>-7,19</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>12,7</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>12,36</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>1,13</t>
-        </is>
-      </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>28,6</t>
+          <t>11,49</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>20,98</t>
+          <t>20,13</t>
         </is>
       </c>
     </row>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-8,87; 12,1</t>
+          <t>2,73; 23,25</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-17,88; 3,01</t>
+          <t>-9,28; 10,66</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-9,17; 31,81</t>
+          <t>11,03; 44,49</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>1,83; 22,27</t>
+          <t>-9,3; 12,31</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-9,36; 10,36</t>
+          <t>-17,39; 2,57</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>9,9; 43,78</t>
+          <t>-7,56; 32,1</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,46; 14,81</t>
+          <t>-0,45; 14,6</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-9,46; 4,88</t>
+          <t>-9,83; 5,28</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>7,99; 33,8</t>
+          <t>5,8; 32,23</t>
         </is>
       </c>
     </row>
@@ -730,32 +730,32 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>35,43%</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>3,25%</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>81,45%</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
           <t>3,43%</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="G6" s="2" t="inlineStr">
         <is>
           <t>-16,06%</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>28,37%</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>35,43%</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>3,25%</t>
-        </is>
-      </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>81,98%</t>
+          <t>25,67%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>52,86%</t>
+          <t>50,71%</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-17,51; 31,24</t>
+          <t>6,87; 78,99</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-34,92; 8,04</t>
+          <t>-23,02; 36,28</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-17,87; 76,75</t>
+          <t>27,23; 143,36</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>4,04; 75,31</t>
+          <t>-17,67; 32,09</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-23,12; 34,46</t>
+          <t>-35,6; 6,46</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>27,73; 143,56</t>
+          <t>-15,89; 78,97</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>1,05; 41,44</t>
+          <t>-0,76; 42,47</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-21,94; 13,28</t>
+          <t>-22,56; 15,43</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>19,2; 92,22</t>
+          <t>14,5; 87,17</t>
         </is>
       </c>
     </row>
@@ -840,32 +840,32 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>0,41</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>-0,42</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>14,23</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
           <t>3,71</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr">
         <is>
           <t>8,84</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>23,87</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>0,41</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>-0,42</t>
-        </is>
-      </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>14,82</t>
+          <t>22,41</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>19,21</t>
+          <t>18,24</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-3,39; 11,91</t>
+          <t>-6,79; 6,82</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1,66; 16,48</t>
+          <t>-7,47; 6,59</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>9,16; 34,01</t>
+          <t>-1,38; 25,38</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-6,98; 7,19</t>
+          <t>-4,24; 10,29</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-7,74; 6,29</t>
+          <t>1,88; 16,1</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,36; 24,99</t>
+          <t>8,8; 34,28</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-2,89; 6,75</t>
+          <t>-2,78; 7,33</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-0,65; 9,38</t>
+          <t>-0,69; 9,85</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>10,12; 26,65</t>
+          <t>9,28; 26,45</t>
         </is>
       </c>
     </row>
@@ -946,32 +946,32 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>0,61%</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>-0,62%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>21,05%</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
           <t>6,07%</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="G10" s="2" t="inlineStr">
         <is>
           <t>14,44%</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>39,0%</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>0,61%</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>-0,62%</t>
-        </is>
-      </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>21,92%</t>
+          <t>36,62%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>29,83%</t>
+          <t>28,33%</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-4,83; 21,21</t>
+          <t>-9,5; 10,58</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>2,48; 28,43</t>
+          <t>-10,49; 10,15</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>16,62; 59,89</t>
+          <t>-0,55; 39,4</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-9,64; 11,17</t>
+          <t>-6,73; 18,13</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-10,8; 9,69</t>
+          <t>2,9; 28,19</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0,58; 38,07</t>
+          <t>13,73; 59,2</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-4,35; 10,69</t>
+          <t>-4,25; 11,8</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-0,86; 15,39</t>
+          <t>-0,99; 15,88</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>15,57; 43,24</t>
+          <t>14,2; 41,87</t>
         </is>
       </c>
     </row>
@@ -1056,32 +1056,32 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>1,54</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>3,1</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>11,29</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
           <t>5,54</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="G12" s="2" t="inlineStr">
         <is>
           <t>5,52</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>12,25</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>1,54</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>3,1</t>
-        </is>
-      </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>11,75</t>
+          <t>9,9</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>12,1</t>
+          <t>10,81</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-3,82; 15,48</t>
+          <t>-7,79; 10,74</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-3,48; 15,36</t>
+          <t>-5,48; 11,5</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-3,38; 25,63</t>
+          <t>-3,56; 22,38</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-7,24; 10,63</t>
+          <t>-4,53; 14,98</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-5,55; 11,93</t>
+          <t>-3,86; 14,28</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-2,09; 21,92</t>
+          <t>-6,26; 24,71</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-3,02; 10,03</t>
+          <t>-3,23; 10,16</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-2,28; 10,62</t>
+          <t>-1,91; 10,67</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>0,87; 21,33</t>
+          <t>0,1; 20,71</t>
         </is>
       </c>
     </row>
@@ -1162,32 +1162,32 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>2,14%</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>4,32%</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>15,73%</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
           <t>8,45%</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="G14" s="2" t="inlineStr">
         <is>
           <t>8,41%</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>18,67%</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>2,14%</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>4,32%</t>
-        </is>
-      </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>16,38%</t>
+          <t>15,09%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>17,58%</t>
+          <t>15,71%</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-5,43; 25,84</t>
+          <t>-10,0; 16,1</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-4,89; 26,48</t>
+          <t>-6,99; 17,08</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-4,89; 42,72</t>
+          <t>-4,63; 32,98</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-9,43; 16,28</t>
+          <t>-6,26; 25,18</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-7,18; 17,58</t>
+          <t>-5,55; 24,0</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-2,68; 32,68</t>
+          <t>-9,23; 39,65</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-4,17; 15,55</t>
+          <t>-4,52; 15,55</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-3,13; 16,61</t>
+          <t>-2,64; 16,39</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>1,45; 32,73</t>
+          <t>0,14; 31,16</t>
         </is>
       </c>
     </row>
@@ -1272,32 +1272,32 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>-1,99</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>-0,72</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>6,34</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
           <t>2,44</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="G16" s="2" t="inlineStr">
         <is>
           <t>-0,13</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>5,15</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>-1,99</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>-0,72</t>
-        </is>
-      </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>6,92</t>
+          <t>4,15</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>6,13</t>
+          <t>5,39</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-5,1; 10,89</t>
+          <t>-10,79; 5,53</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-7,89; 8,95</t>
+          <t>-9,08; 7,32</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-13,12; 18,4</t>
+          <t>-8,31; 16,3</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-9,52; 6,32</t>
+          <t>-6,11; 10,37</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-8,38; 8,52</t>
+          <t>-7,59; 8,47</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-5,56; 17,56</t>
+          <t>-15,13; 17,84</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-5,43; 6,0</t>
+          <t>-5,59; 5,57</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-5,67; 5,45</t>
+          <t>-6,32; 5,11</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-3,61; 15,53</t>
+          <t>-4,83; 13,75</t>
         </is>
       </c>
     </row>
@@ -1378,32 +1378,32 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>-2,7%</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>-0,98%</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>8,61%</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
           <t>3,26%</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="G18" s="2" t="inlineStr">
         <is>
           <t>-0,17%</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>6,88%</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>-2,7%</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>-0,98%</t>
-        </is>
-      </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>9,39%</t>
+          <t>5,54%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>8,26%</t>
+          <t>7,25%</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-6,63; 15,51</t>
+          <t>-14,16; 7,68</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-10,19; 12,83</t>
+          <t>-11,6; 10,36</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-16,39; 25,72</t>
+          <t>-10,02; 22,83</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-12,33; 9,06</t>
+          <t>-7,63; 14,42</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-10,79; 12,23</t>
+          <t>-9,67; 12,2</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-6,99; 25,08</t>
+          <t>-19,43; 24,38</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-7,14; 8,38</t>
+          <t>-7,2; 7,79</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-7,54; 7,62</t>
+          <t>-8,31; 7,07</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-4,61; 21,69</t>
+          <t>-6,58; 18,6</t>
         </is>
       </c>
     </row>
@@ -1488,32 +1488,32 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>1,47</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>0,53</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>14,87</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
           <t>2,41</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="G20" s="2" t="inlineStr">
         <is>
           <t>2,26</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>14,29</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>1,47</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>0,53</t>
-        </is>
-      </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>15,12</t>
+          <t>12,75</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>14,85</t>
+          <t>14,02</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-2,13; 6,94</t>
+          <t>-2,68; 5,79</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-1,84; 6,97</t>
+          <t>-4,07; 4,65</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>5,84; 21,44</t>
+          <t>7,8; 21,15</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-2,84; 5,89</t>
+          <t>-2,24; 6,68</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-3,48; 4,77</t>
+          <t>-2,03; 6,82</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>8,61; 21,31</t>
+          <t>3,9; 20,14</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-1,12; 4,85</t>
+          <t>-1,24; 4,86</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-1,65; 4,18</t>
+          <t>-1,62; 4,55</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>9,58; 20,05</t>
+          <t>8,23; 18,7</t>
         </is>
       </c>
     </row>
@@ -1594,32 +1594,32 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>2,28%</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>0,83%</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>23,11%</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
           <t>3,84%</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="G22" s="2" t="inlineStr">
         <is>
           <t>3,6%</t>
         </is>
       </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>22,75%</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>2,28%</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
-        <is>
-          <t>0,83%</t>
-        </is>
-      </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>23,5%</t>
+          <t>20,3%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -1634,7 +1634,7 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>23,35%</t>
+          <t>22,04%</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-3,29; 11,35</t>
+          <t>-4,09; 9,29</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-2,84; 11,62</t>
+          <t>-6,16; 7,54</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>9,32; 35,39</t>
+          <t>11,66; 33,85</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-4,27; 9,44</t>
+          <t>-3,44; 10,87</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-5,33; 7,64</t>
+          <t>-3,09; 11,3</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>13,08; 34,03</t>
+          <t>6,21; 33,29</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-1,7; 7,83</t>
+          <t>-1,9; 7,83</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-2,56; 6,7</t>
+          <t>-2,5; 7,31</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>14,58; 31,81</t>
+          <t>12,82; 29,97</t>
         </is>
       </c>
     </row>
